--- a/MMCL_OpenCLIP_ViT-B16_LAION-400M_Baselines.xlsx
+++ b/MMCL_OpenCLIP_ViT-B16_LAION-400M_Baselines.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="14725"/>
+    <workbookView windowHeight="14725" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Seed0" sheetId="1" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="1" xr9:uid="{694E5D8E-03C0-4347-9BEF-78E71558AF81}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="1" xr9:uid="{E416C66E-CEF2-4491-A605-30848C13FD56}">
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
@@ -1689,10 +1689,18 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="H11" s="8">
+        <v>92.38</v>
+      </c>
+      <c r="I11" s="8">
+        <v>88.08</v>
+      </c>
+      <c r="J11" s="8">
+        <v>91.24</v>
+      </c>
+      <c r="K11" s="8">
+        <v>89.57</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -1712,10 +1720,18 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="H12" s="8">
+        <v>86.16</v>
+      </c>
+      <c r="I12" s="8">
+        <v>78.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>84.11</v>
+      </c>
+      <c r="K12" s="8">
+        <v>78.44</v>
+      </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -1925,20 +1941,36 @@
       <c r="E17" s="10">
         <v>58.75</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="9">
+        <v>66.09</v>
+      </c>
+      <c r="G17" s="9">
+        <v>62.65</v>
+      </c>
       <c r="H17" s="9">
         <v>87.41</v>
       </c>
       <c r="I17" s="9">
         <v>82.63</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="J17" s="9">
+        <v>85.86</v>
+      </c>
+      <c r="K17" s="9">
+        <v>83.07</v>
+      </c>
+      <c r="L17" s="9">
+        <v>95.46</v>
+      </c>
+      <c r="M17" s="9">
+        <v>90.37</v>
+      </c>
+      <c r="N17" s="9">
+        <v>93.95</v>
+      </c>
+      <c r="O17" s="9">
+        <v>91.11</v>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15">
       <c r="A18" s="11"/>
@@ -2389,14 +2421,30 @@
       <c r="C29" s="7">
         <v>2024</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+      <c r="D29" s="8">
+        <v>82.97</v>
+      </c>
+      <c r="E29" s="8">
+        <v>80.02</v>
+      </c>
+      <c r="F29" s="8">
+        <v>82.35</v>
+      </c>
+      <c r="G29" s="8">
+        <v>80.82</v>
+      </c>
+      <c r="H29" s="8">
+        <v>85.41</v>
+      </c>
+      <c r="I29" s="8">
+        <v>84.61</v>
+      </c>
+      <c r="J29" s="8">
+        <v>84.51</v>
+      </c>
+      <c r="K29" s="8">
+        <v>84.78</v>
+      </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -2412,14 +2460,30 @@
       <c r="C30" s="7">
         <v>2024</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
+      <c r="D30" s="8">
+        <v>85.07</v>
+      </c>
+      <c r="E30" s="8">
+        <v>79.42</v>
+      </c>
+      <c r="F30" s="8">
+        <v>84.02</v>
+      </c>
+      <c r="G30" s="8">
+        <v>81.45</v>
+      </c>
+      <c r="H30" s="8">
+        <v>71.14</v>
+      </c>
+      <c r="I30" s="8">
+        <v>58.72</v>
+      </c>
+      <c r="J30" s="8">
+        <v>67.56</v>
+      </c>
+      <c r="K30" s="8">
+        <v>60.42</v>
+      </c>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -2670,18 +2734,42 @@
       <c r="C36" s="9">
         <v>2026</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="D36" s="9">
+        <v>85.21</v>
+      </c>
+      <c r="E36" s="9">
+        <v>80.2</v>
+      </c>
+      <c r="F36" s="9">
+        <v>82.34</v>
+      </c>
+      <c r="G36" s="9">
+        <v>80.35</v>
+      </c>
+      <c r="H36" s="9">
+        <v>87.4</v>
+      </c>
+      <c r="I36" s="9">
+        <v>81.85</v>
+      </c>
+      <c r="J36" s="9">
+        <v>85.46</v>
+      </c>
+      <c r="K36" s="9">
+        <v>81.59</v>
+      </c>
+      <c r="L36" s="9">
+        <v>95.25</v>
+      </c>
+      <c r="M36" s="9">
+        <v>92.61</v>
+      </c>
+      <c r="N36" s="9">
+        <v>95.76</v>
+      </c>
+      <c r="O36" s="9">
+        <v>93.6</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:15">
       <c r="A37" s="9"/>
@@ -3447,18 +3535,42 @@
       <c r="C57" s="9">
         <v>2026</v>
       </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
+      <c r="D57" s="14">
+        <v>87.05</v>
+      </c>
+      <c r="E57" s="14">
+        <v>80.18</v>
+      </c>
+      <c r="F57" s="14">
+        <v>84.66</v>
+      </c>
+      <c r="G57" s="14">
+        <v>81.01</v>
+      </c>
+      <c r="H57" s="14">
+        <v>89.8</v>
+      </c>
+      <c r="I57" s="14">
+        <v>82.56</v>
+      </c>
+      <c r="J57" s="14">
+        <v>88.91</v>
+      </c>
+      <c r="K57" s="14">
+        <v>86.27</v>
+      </c>
+      <c r="L57" s="14">
+        <v>57.35</v>
+      </c>
+      <c r="M57" s="14">
+        <v>46.98</v>
+      </c>
+      <c r="N57" s="14">
+        <v>50.52</v>
+      </c>
+      <c r="O57" s="14">
+        <v>44.25</v>
+      </c>
     </row>
     <row r="58" ht="17.55" customHeight="1" spans="1:15">
       <c r="A58" s="9"/>
@@ -3945,10 +4057,18 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="H10" s="8">
+        <v>92.38</v>
+      </c>
+      <c r="I10" s="8">
+        <v>88.2</v>
+      </c>
+      <c r="J10" s="8">
+        <v>91.05</v>
+      </c>
+      <c r="K10" s="8">
+        <v>88.72</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -3968,10 +4088,18 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="H11" s="8">
+        <v>85.88</v>
+      </c>
+      <c r="I11" s="8">
+        <v>77.44</v>
+      </c>
+      <c r="J11" s="8">
+        <v>84.33</v>
+      </c>
+      <c r="K11" s="8">
+        <v>77.57</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -4222,18 +4350,42 @@
       <c r="C17" s="9">
         <v>2026</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="D17" s="8">
+        <v>69.4</v>
+      </c>
+      <c r="E17" s="8">
+        <v>61</v>
+      </c>
+      <c r="F17" s="8">
+        <v>65.11</v>
+      </c>
+      <c r="G17" s="8">
+        <v>62.5</v>
+      </c>
+      <c r="H17" s="8">
+        <v>86.06</v>
+      </c>
+      <c r="I17" s="8">
+        <v>81.46</v>
+      </c>
+      <c r="J17" s="8">
+        <v>84.82</v>
+      </c>
+      <c r="K17" s="8">
+        <v>83.47</v>
+      </c>
+      <c r="L17" s="8">
+        <v>94.15</v>
+      </c>
+      <c r="M17" s="8">
+        <v>90.45</v>
+      </c>
+      <c r="N17" s="8">
+        <v>93.11</v>
+      </c>
+      <c r="O17" s="8">
+        <v>90.96</v>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1" spans="1:15">
       <c r="A18" s="11"/>
@@ -4684,14 +4836,30 @@
       <c r="C29" s="7">
         <v>2024</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+      <c r="D29" s="8">
+        <v>83.04</v>
+      </c>
+      <c r="E29" s="8">
+        <v>80.66</v>
+      </c>
+      <c r="F29" s="8">
+        <v>82.39</v>
+      </c>
+      <c r="G29" s="8">
+        <v>81</v>
+      </c>
+      <c r="H29" s="8">
+        <v>85.51</v>
+      </c>
+      <c r="I29" s="8">
+        <v>85.11</v>
+      </c>
+      <c r="J29" s="8">
+        <v>84.2</v>
+      </c>
+      <c r="K29" s="8">
+        <v>84.52</v>
+      </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -4707,14 +4875,30 @@
       <c r="C30" s="7">
         <v>2024</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
+      <c r="D30" s="8">
+        <v>84.85</v>
+      </c>
+      <c r="E30" s="8">
+        <v>79.3</v>
+      </c>
+      <c r="F30" s="8">
+        <v>84.03</v>
+      </c>
+      <c r="G30" s="8">
+        <v>81.15</v>
+      </c>
+      <c r="H30" s="8">
+        <v>71.25</v>
+      </c>
+      <c r="I30" s="8">
+        <v>58.66</v>
+      </c>
+      <c r="J30" s="8">
+        <v>68.15</v>
+      </c>
+      <c r="K30" s="8">
+        <v>61.13</v>
+      </c>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -4965,18 +5149,42 @@
       <c r="C36" s="9">
         <v>2026</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="D36" s="9">
+        <v>85.6</v>
+      </c>
+      <c r="E36" s="9">
+        <v>81.08</v>
+      </c>
+      <c r="F36" s="9">
+        <v>83.19</v>
+      </c>
+      <c r="G36" s="9">
+        <v>81.4</v>
+      </c>
+      <c r="H36" s="9">
+        <v>86.52</v>
+      </c>
+      <c r="I36" s="9">
+        <v>80.92</v>
+      </c>
+      <c r="J36" s="9">
+        <v>84.2</v>
+      </c>
+      <c r="K36" s="9">
+        <v>81.85</v>
+      </c>
+      <c r="L36" s="9">
+        <v>95.39</v>
+      </c>
+      <c r="M36" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="N36" s="9">
+        <v>95.02</v>
+      </c>
+      <c r="O36" s="9">
+        <v>92.76</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:15">
       <c r="A37" s="9"/>
@@ -5725,18 +5933,42 @@
       <c r="C56" s="9">
         <v>2026</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
+      <c r="D56" s="8">
+        <v>86.37</v>
+      </c>
+      <c r="E56" s="8">
+        <v>80.15</v>
+      </c>
+      <c r="F56" s="8">
+        <v>83.93</v>
+      </c>
+      <c r="G56" s="8">
+        <v>81.24</v>
+      </c>
+      <c r="H56" s="8">
+        <v>89.53</v>
+      </c>
+      <c r="I56" s="8">
+        <v>85.67</v>
+      </c>
+      <c r="J56" s="8">
+        <v>88.32</v>
+      </c>
+      <c r="K56" s="8">
+        <v>86.13</v>
+      </c>
+      <c r="L56" s="8">
+        <v>56.85</v>
+      </c>
+      <c r="M56" s="8">
+        <v>46.64</v>
+      </c>
+      <c r="N56" s="8">
+        <v>52.05</v>
+      </c>
+      <c r="O56" s="8">
+        <v>48.05</v>
+      </c>
     </row>
     <row r="57" ht="17.55" customHeight="1"/>
     <row r="58" ht="17.55" customHeight="1"/>
@@ -6206,10 +6438,18 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="H10" s="8">
+        <v>92.44</v>
+      </c>
+      <c r="I10" s="8">
+        <v>88.22</v>
+      </c>
+      <c r="J10" s="8">
+        <v>91.2</v>
+      </c>
+      <c r="K10" s="8">
+        <v>89.03</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -6229,10 +6469,18 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="H11" s="8">
+        <v>86.19</v>
+      </c>
+      <c r="I11" s="8">
+        <v>76.35</v>
+      </c>
+      <c r="J11" s="8">
+        <v>84.59</v>
+      </c>
+      <c r="K11" s="8">
+        <v>78.74</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -7016,14 +7264,30 @@
       <c r="C30" s="7">
         <v>2024</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
+      <c r="D30" s="8">
+        <v>83.12</v>
+      </c>
+      <c r="E30" s="8">
+        <v>80.48</v>
+      </c>
+      <c r="F30" s="8">
+        <v>82.26</v>
+      </c>
+      <c r="G30" s="8">
+        <v>81.13</v>
+      </c>
+      <c r="H30" s="8">
+        <v>85.74</v>
+      </c>
+      <c r="I30" s="8">
+        <v>84.4</v>
+      </c>
+      <c r="J30" s="8">
+        <v>84.58</v>
+      </c>
+      <c r="K30" s="8">
+        <v>84.98</v>
+      </c>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -7039,14 +7303,30 @@
       <c r="C31" s="7">
         <v>2024</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
+      <c r="D31" s="8">
+        <v>84.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>79.85</v>
+      </c>
+      <c r="F31" s="8">
+        <v>84.2</v>
+      </c>
+      <c r="G31" s="8">
+        <v>81.52</v>
+      </c>
+      <c r="H31" s="8">
+        <v>71.3</v>
+      </c>
+      <c r="I31" s="8">
+        <v>58.94</v>
+      </c>
+      <c r="J31" s="8">
+        <v>68.37</v>
+      </c>
+      <c r="K31" s="8">
+        <v>61.37</v>
+      </c>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
@@ -8015,8 +8295,12 @@
       <c r="M55" s="8">
         <v>44.61</v>
       </c>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
+      <c r="N55" s="8">
+        <v>53.6</v>
+      </c>
+      <c r="O55" s="8">
+        <v>47.33</v>
+      </c>
     </row>
     <row r="56" ht="17.55" customHeight="1"/>
     <row r="57" ht="17.55" customHeight="1"/>
@@ -8340,18 +8624,42 @@
       <c r="C7" s="7">
         <v>2023</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="D7" s="8">
+        <v>68.83</v>
+      </c>
+      <c r="E7" s="8">
+        <v>61.96</v>
+      </c>
+      <c r="F7" s="8">
+        <v>66.48</v>
+      </c>
+      <c r="G7" s="8">
+        <v>61.78</v>
+      </c>
+      <c r="H7" s="8">
+        <v>89.42</v>
+      </c>
+      <c r="I7" s="8">
+        <v>84.41</v>
+      </c>
+      <c r="J7" s="8">
+        <v>85.96</v>
+      </c>
+      <c r="K7" s="8">
+        <v>83.46</v>
+      </c>
+      <c r="L7" s="8">
+        <v>94.35</v>
+      </c>
+      <c r="M7" s="8">
+        <v>90.45</v>
+      </c>
+      <c r="N7" s="8">
+        <v>92.8</v>
+      </c>
+      <c r="O7" s="8">
+        <v>89.69</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:15">
       <c r="A8" s="7" t="s">
@@ -8363,18 +8671,42 @@
       <c r="C8" s="7">
         <v>2023</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
+      <c r="D8" s="8">
+        <v>56.27</v>
+      </c>
+      <c r="E8" s="8">
+        <v>47.4</v>
+      </c>
+      <c r="F8" s="8">
+        <v>53.58</v>
+      </c>
+      <c r="G8" s="8">
+        <v>48.42</v>
+      </c>
+      <c r="H8" s="8">
+        <v>82.65</v>
+      </c>
+      <c r="I8" s="8">
+        <v>75.76</v>
+      </c>
+      <c r="J8" s="8">
+        <v>73.13</v>
+      </c>
+      <c r="K8" s="8">
+        <v>68.49</v>
+      </c>
+      <c r="L8" s="8">
+        <v>91.67</v>
+      </c>
+      <c r="M8" s="8">
+        <v>86.31</v>
+      </c>
+      <c r="N8" s="8">
+        <v>89.54</v>
+      </c>
+      <c r="O8" s="8">
+        <v>86.77</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:15">
       <c r="A9" s="7" t="s">
@@ -8437,10 +8769,18 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="H10" s="8">
+        <v>92.46</v>
+      </c>
+      <c r="I10" s="8">
+        <v>88.2</v>
+      </c>
+      <c r="J10" s="8">
+        <v>90.92</v>
+      </c>
+      <c r="K10" s="8">
+        <v>89.02</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -8460,10 +8800,18 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="H11" s="8">
+        <v>85.72</v>
+      </c>
+      <c r="I11" s="8">
+        <v>76.75</v>
+      </c>
+      <c r="J11" s="8">
+        <v>84.01</v>
+      </c>
+      <c r="K11" s="8">
+        <v>78.88</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -8720,24 +9068,36 @@
       <c r="E17" s="10">
         <v>56.59</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="9">
+        <v>67.24</v>
+      </c>
+      <c r="G17" s="9">
+        <v>62.86</v>
+      </c>
       <c r="H17" s="9">
         <v>88.18</v>
       </c>
       <c r="I17" s="9">
         <v>82.29</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="J17" s="9">
+        <v>85.56</v>
+      </c>
+      <c r="K17" s="9">
+        <v>83.16</v>
+      </c>
       <c r="L17" s="9">
         <v>94.4</v>
       </c>
       <c r="M17" s="9">
         <v>90.62</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="N17" s="9">
+        <v>93.04</v>
+      </c>
+      <c r="O17" s="9">
+        <v>91.13</v>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15">
       <c r="A18" s="11"/>
@@ -9047,18 +9407,42 @@
       <c r="C26" s="7">
         <v>2023</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
+      <c r="D26" s="8">
+        <v>84.72</v>
+      </c>
+      <c r="E26" s="8">
+        <v>79.45</v>
+      </c>
+      <c r="F26" s="8">
+        <v>82.72</v>
+      </c>
+      <c r="G26" s="8">
+        <v>80.87</v>
+      </c>
+      <c r="H26" s="8">
+        <v>87.31</v>
+      </c>
+      <c r="I26" s="8">
+        <v>80.75</v>
+      </c>
+      <c r="J26" s="8">
+        <v>85.97</v>
+      </c>
+      <c r="K26" s="8">
+        <v>81.59</v>
+      </c>
+      <c r="L26" s="8">
+        <v>41.38</v>
+      </c>
+      <c r="M26" s="8">
+        <v>97.57</v>
+      </c>
+      <c r="N26" s="8">
+        <v>33.87</v>
+      </c>
+      <c r="O26" s="8">
+        <v>97.39</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:15">
       <c r="A27" s="7" t="s">
@@ -9070,18 +9454,42 @@
       <c r="C27" s="7">
         <v>2023</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
+      <c r="D27" s="8">
+        <v>74.19</v>
+      </c>
+      <c r="E27" s="8">
+        <v>66.65</v>
+      </c>
+      <c r="F27" s="8">
+        <v>73.04</v>
+      </c>
+      <c r="G27" s="8">
+        <v>70.08</v>
+      </c>
+      <c r="H27" s="8">
+        <v>82.93</v>
+      </c>
+      <c r="I27" s="8">
+        <v>75.19</v>
+      </c>
+      <c r="J27" s="8">
+        <v>80.92</v>
+      </c>
+      <c r="K27" s="8">
+        <v>76.38</v>
+      </c>
+      <c r="L27" s="8">
+        <v>91.79</v>
+      </c>
+      <c r="M27" s="8">
+        <v>86.21</v>
+      </c>
+      <c r="N27" s="8">
+        <v>88.58</v>
+      </c>
+      <c r="O27" s="8">
+        <v>86.06</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:15">
       <c r="A28" s="7" t="s">
@@ -9140,14 +9548,30 @@
       <c r="C29" s="7">
         <v>2024</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+      <c r="D29" s="8">
+        <v>83.09</v>
+      </c>
+      <c r="E29" s="8">
+        <v>80.34</v>
+      </c>
+      <c r="F29" s="8">
+        <v>82.55</v>
+      </c>
+      <c r="G29" s="8">
+        <v>80.9</v>
+      </c>
+      <c r="H29" s="8">
+        <v>85.7</v>
+      </c>
+      <c r="I29" s="8">
+        <v>84.98</v>
+      </c>
+      <c r="J29" s="8">
+        <v>84.34</v>
+      </c>
+      <c r="K29" s="8">
+        <v>85.12</v>
+      </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -9163,14 +9587,30 @@
       <c r="C30" s="7">
         <v>2024</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
+      <c r="D30" s="8">
+        <v>85.12</v>
+      </c>
+      <c r="E30" s="8">
+        <v>79.2</v>
+      </c>
+      <c r="F30" s="8">
+        <v>84.38</v>
+      </c>
+      <c r="G30" s="8">
+        <v>81.58</v>
+      </c>
+      <c r="H30" s="8">
+        <v>71.2</v>
+      </c>
+      <c r="I30" s="8">
+        <v>58.68</v>
+      </c>
+      <c r="J30" s="8">
+        <v>67.75</v>
+      </c>
+      <c r="K30" s="8">
+        <v>60.53</v>
+      </c>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -9327,8 +9767,12 @@
       <c r="C34" s="7">
         <v>2025</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="D34" s="8">
+        <v>84.48</v>
+      </c>
+      <c r="E34" s="8">
+        <v>77.92</v>
+      </c>
       <c r="F34" s="8">
         <v>81.64</v>
       </c>
@@ -9423,24 +9867,36 @@
       <c r="E36" s="9">
         <v>75.27</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="9">
+        <v>83.21</v>
+      </c>
+      <c r="G36" s="9">
+        <v>80.92</v>
+      </c>
       <c r="H36" s="9">
         <v>86.82</v>
       </c>
       <c r="I36" s="9">
         <v>80.75</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
+      <c r="J36" s="9">
+        <v>85.65</v>
+      </c>
+      <c r="K36" s="9">
+        <v>82.06</v>
+      </c>
       <c r="L36" s="9">
         <v>95.69</v>
       </c>
       <c r="M36" s="9">
         <v>93.26</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="N36" s="9">
+        <v>94.86</v>
+      </c>
+      <c r="O36" s="9">
+        <v>92.88</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:15">
       <c r="A37" s="9"/>
@@ -9750,18 +10206,42 @@
       <c r="C45" s="7">
         <v>2023</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
+      <c r="D45" s="8">
+        <v>88.92</v>
+      </c>
+      <c r="E45" s="8">
+        <v>82.37</v>
+      </c>
+      <c r="F45" s="8">
+        <v>84.38</v>
+      </c>
+      <c r="G45" s="8">
+        <v>81.18</v>
+      </c>
+      <c r="H45" s="8">
+        <v>89.4</v>
+      </c>
+      <c r="I45" s="8">
+        <v>85.08</v>
+      </c>
+      <c r="J45" s="8">
+        <v>86.6</v>
+      </c>
+      <c r="K45" s="8">
+        <v>84.93</v>
+      </c>
+      <c r="L45" s="8">
+        <v>56.31</v>
+      </c>
+      <c r="M45" s="8">
+        <v>47.44</v>
+      </c>
+      <c r="N45" s="8">
+        <v>61.52</v>
+      </c>
+      <c r="O45" s="8">
+        <v>57.05</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:15">
       <c r="A46" s="7" t="s">
@@ -9773,18 +10253,42 @@
       <c r="C46" s="7">
         <v>2023</v>
       </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
+      <c r="D46" s="8">
+        <v>83.61</v>
+      </c>
+      <c r="E46" s="8">
+        <v>75.41</v>
+      </c>
+      <c r="F46" s="8">
+        <v>73.84</v>
+      </c>
+      <c r="G46" s="8">
+        <v>69.56</v>
+      </c>
+      <c r="H46" s="8">
+        <v>81.61</v>
+      </c>
+      <c r="I46" s="8">
+        <v>75.79</v>
+      </c>
+      <c r="J46" s="8">
+        <v>73.97</v>
+      </c>
+      <c r="K46" s="8">
+        <v>71.02</v>
+      </c>
+      <c r="L46" s="8">
+        <v>47.63</v>
+      </c>
+      <c r="M46" s="8">
+        <v>38.65</v>
+      </c>
+      <c r="N46" s="8">
+        <v>52.66</v>
+      </c>
+      <c r="O46" s="8">
+        <v>48.4</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:15">
       <c r="A47" s="7" t="s">
@@ -10130,24 +10634,36 @@
       <c r="E55" s="8">
         <v>79.88</v>
       </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
+      <c r="F55" s="8">
+        <v>84.93</v>
+      </c>
+      <c r="G55" s="8">
+        <v>81.01</v>
+      </c>
       <c r="H55" s="8">
         <v>87.3</v>
       </c>
       <c r="I55" s="8">
         <v>81.62</v>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
+      <c r="J55" s="8">
+        <v>87.89</v>
+      </c>
+      <c r="K55" s="8">
+        <v>86.12</v>
+      </c>
       <c r="L55" s="8">
         <v>56.16</v>
       </c>
       <c r="M55" s="8">
         <v>43.6</v>
       </c>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
+      <c r="N55" s="8">
+        <v>52.56</v>
+      </c>
+      <c r="O55" s="8">
+        <v>48.04</v>
+      </c>
     </row>
     <row r="56" ht="17.55" customHeight="1"/>
     <row r="57" ht="17.55" customHeight="1"/>
